--- a/data/trans_orig/POLIPATOLOGIA_Lim_5-Clase-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_Lim_5-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2012</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>6387</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21913</t>
+          <t>23109</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7578</t>
+          <t>7817</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23274</t>
+          <t>23721</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>431902</t>
+          <t>431258</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>292541</t>
+          <t>291345</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>307329</t>
+          <t>308067</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>728391</t>
+          <t>727944</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>744087</t>
+          <t>743848</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15281</t>
+          <t>15593</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24794</t>
+          <t>24985</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14800</t>
+          <t>14564</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35352</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>403516</t>
+          <t>403204</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>414847</t>
+          <t>414771</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313217</t>
+          <t>313026</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>330319</t>
+          <t>329365</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>721456</t>
+          <t>722097</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>742008</t>
+          <t>742244</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18811</t>
+          <t>19145</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41886</t>
+          <t>42816</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9629</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25096</t>
+          <t>25828</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33835</t>
+          <t>33758</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61254</t>
+          <t>60248</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>587529</t>
+          <t>586599</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>610604</t>
+          <t>610270</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>235033</t>
+          <t>234301</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>250500</t>
+          <t>250217</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>828290</t>
+          <t>829296</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>855709</t>
+          <t>855786</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49762</t>
+          <t>48987</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81525</t>
+          <t>81865</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32707</t>
+          <t>33076</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60399</t>
+          <t>60285</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90045</t>
+          <t>88431</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133609</t>
+          <t>131547</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1077484</t>
+          <t>1077144</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1109247</t>
+          <t>1110022</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>706258</t>
+          <t>706372</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>733950</t>
+          <t>733581</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1792058</t>
+          <t>1794120</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1835622</t>
+          <t>1837236</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11615</t>
+          <t>10532</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28494</t>
+          <t>27811</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>78185</t>
+          <t>79017</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>116148</t>
+          <t>118684</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>94561</t>
+          <t>95227</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135966</t>
+          <t>136900</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>482102</t>
+          <t>482785</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>498981</t>
+          <t>500064</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>645374</t>
+          <t>642838</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>683337</t>
+          <t>682505</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1136152</t>
+          <t>1135218</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1177557</t>
+          <t>1176891</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,51%</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>7826</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>124442</t>
+          <t>120365</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>170260</t>
+          <t>169680</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>122725</t>
+          <t>125626</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>171930</t>
+          <t>170994</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>260580</t>
+          <t>259056</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>939091</t>
+          <t>939671</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>984909</t>
+          <t>988986</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1204303</t>
+          <t>1205239</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1253508</t>
+          <t>1250607</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,87%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>99698</t>
+          <t>101221</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>146012</t>
+          <t>147631</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>296300</t>
+          <t>292109</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>368916</t>
+          <t>367271</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>412578</t>
+          <t>406276</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>503049</t>
+          <t>493248</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3275898</t>
+          <t>3274279</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3322212</t>
+          <t>3320689</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3181209</t>
+          <t>3182854</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3253825</t>
+          <t>3258016</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6468986</t>
+          <t>6478787</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6559457</t>
+          <t>6565759</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2016</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21854</t>
+          <t>22289</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24351</t>
+          <t>26161</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19034</t>
+          <t>19411</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41673</t>
+          <t>41600</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>407238</t>
+          <t>406803</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>422653</t>
+          <t>422415</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>322704</t>
+          <t>320894</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>338453</t>
+          <t>337759</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>734474</t>
+          <t>734547</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>757113</t>
+          <t>756736</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12288</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5806</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21245</t>
+          <t>20680</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9488</t>
+          <t>9893</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27835</t>
+          <t>27954</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>364939</t>
+          <t>364675</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>375309</t>
+          <t>375270</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>351028</t>
+          <t>351593</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>366467</t>
+          <t>367031</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>721665</t>
+          <t>721546</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>740012</t>
+          <t>739607</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6896</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21854</t>
+          <t>21641</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15712</t>
+          <t>15553</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35691</t>
+          <t>35737</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26425</t>
+          <t>26882</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50312</t>
+          <t>51974</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>500060</t>
+          <t>500273</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515018</t>
+          <t>515022</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>130432</t>
+          <t>130386</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>150411</t>
+          <t>150570</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>637724</t>
+          <t>636062</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>661611</t>
+          <t>661154</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28733</t>
+          <t>28726</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53037</t>
+          <t>53848</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38516</t>
+          <t>37914</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66526</t>
+          <t>67131</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72360</t>
+          <t>73468</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112053</t>
+          <t>110688</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1096601</t>
+          <t>1095790</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1120905</t>
+          <t>1120912</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>759350</t>
+          <t>758745</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>787360</t>
+          <t>787962</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1863461</t>
+          <t>1864826</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1903154</t>
+          <t>1902046</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24423</t>
+          <t>24238</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47981</t>
+          <t>45476</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72457</t>
+          <t>71614</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>109839</t>
+          <t>108328</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>103941</t>
+          <t>104313</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>148723</t>
+          <t>146198</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>572725</t>
+          <t>575230</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>596283</t>
+          <t>596468</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>628405</t>
+          <t>629916</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>665787</t>
+          <t>666630</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1210227</t>
+          <t>1212752</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1255009</t>
+          <t>1254637</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,32%</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>102925</t>
+          <t>101711</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>148630</t>
+          <t>147503</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>104882</t>
+          <t>105080</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>151497</t>
+          <t>147476</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281445</t>
+          <t>280714</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>933395</t>
+          <t>934522</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>979100</t>
+          <t>980314</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1217673</t>
+          <t>1221694</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1264288</t>
+          <t>1264090</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,33%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>87491</t>
+          <t>87037</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>127310</t>
+          <t>125343</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>281043</t>
+          <t>284270</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>353168</t>
+          <t>358850</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>381264</t>
+          <t>380574</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>463498</t>
+          <t>466870</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3258412</t>
+          <t>3260379</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3298231</t>
+          <t>3298685</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3178428</t>
+          <t>3172746</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3250553</t>
+          <t>3247326</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6453820</t>
+          <t>6450448</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6536054</t>
+          <t>6536744</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2023</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11952</t>
+          <t>12055</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27061</t>
+          <t>27320</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30085</t>
+          <t>30318</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50872</t>
+          <t>49494</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>46620</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70678</t>
+          <t>70994</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>478151</t>
+          <t>477892</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>493260</t>
+          <t>493157</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>396595</t>
+          <t>397973</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>417382</t>
+          <t>417149</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>882001</t>
+          <t>881685</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>907394</t>
+          <t>906059</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13329</t>
+          <t>13121</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28955</t>
+          <t>28911</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33669</t>
+          <t>33293</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53811</t>
+          <t>53139</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51637</t>
+          <t>53239</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77841</t>
+          <t>77347</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>423258</t>
+          <t>423302</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>438884</t>
+          <t>439092</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>328769</t>
+          <t>329441</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>348911</t>
+          <t>349287</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>756952</t>
+          <t>757446</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>783156</t>
+          <t>781554</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,62%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>14120</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66864</t>
+          <t>68330</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23813</t>
+          <t>23121</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38753</t>
+          <t>38938</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30937</t>
+          <t>29680</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104324</t>
+          <t>103547</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>601400</t>
+          <t>599934</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>654105</t>
+          <t>654144</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>128158</t>
+          <t>127973</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>143098</t>
+          <t>143790</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>730851</t>
+          <t>731628</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>804238</t>
+          <t>805495</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85623</t>
+          <t>85391</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120803</t>
+          <t>119446</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41531</t>
+          <t>46053</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113751</t>
+          <t>112540</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131721</t>
+          <t>125804</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>214683</t>
+          <t>215155</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>914016</t>
+          <t>915373</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>949196</t>
+          <t>949428</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>864343</t>
+          <t>865554</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>936563</t>
+          <t>932041</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1798229</t>
+          <t>1797757</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1881191</t>
+          <t>1887108</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33376</t>
+          <t>31983</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56457</t>
+          <t>55631</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>128399</t>
+          <t>136699</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>207477</t>
+          <t>210075</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>183293</t>
+          <t>182212</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>252399</t>
+          <t>250407</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>418589</t>
+          <t>419415</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>441670</t>
+          <t>443063</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>633858</t>
+          <t>631260</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>712936</t>
+          <t>704636</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1063982</t>
+          <t>1065974</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1133088</t>
+          <t>1134169</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,16%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8174</t>
+          <t>8561</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>115013</t>
+          <t>115970</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>148077</t>
+          <t>147630</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>118740</t>
+          <t>119699</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>153296</t>
+          <t>153984</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>232333</t>
+          <t>231946</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238882</t>
+          <t>239072</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>613294</t>
+          <t>613741</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>646358</t>
+          <t>645401</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>848582</t>
+          <t>847894</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>883138</t>
+          <t>882179</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>178452</t>
+          <t>174142</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>256450</t>
+          <t>259342</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>405995</t>
+          <t>415797</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>553937</t>
+          <t>556967</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>638292</t>
+          <t>640071</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>795602</t>
+          <t>788847</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3119610</t>
+          <t>3116718</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3197608</t>
+          <t>3201918</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3023821</t>
+          <t>3020791</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3171763</t>
+          <t>3161961</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6158216</t>
+          <t>6164971</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6315526</t>
+          <t>6313747</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/POLIPATOLOGIA_Lim_5-Clase-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_Lim_5-Clase-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>6092</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23109</t>
+          <t>21221</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>7267</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23721</t>
+          <t>23898</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>431258</t>
+          <t>431951</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>291345</t>
+          <t>293233</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308067</t>
+          <t>308362</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>727944</t>
+          <t>727767</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>743848</t>
+          <t>744398</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15593</t>
+          <t>15837</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>8637</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24985</t>
+          <t>24477</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14564</t>
+          <t>14117</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>34902</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>403204</t>
+          <t>402960</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>414771</t>
+          <t>414820</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313026</t>
+          <t>313534</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>329365</t>
+          <t>329374</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>722097</t>
+          <t>721906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>742244</t>
+          <t>742691</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19145</t>
+          <t>18668</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42816</t>
+          <t>41968</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>9604</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25828</t>
+          <t>26138</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,47 +1468,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>10,05%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>45626</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>33909</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>61574</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>3,81%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>9,93%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>45626</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>33758</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>60248</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>586599</t>
+          <t>587447</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>610270</t>
+          <t>610747</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>234301</t>
+          <t>233991</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>250217</t>
+          <t>250525</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,47 +1581,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>96,31%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>794</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>843918</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>827970</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>855635</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>94,87%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>93,08%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>96,19%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>794</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>843918</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>829296</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>855786</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>94,87%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>93,23%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48987</t>
+          <t>50399</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81865</t>
+          <t>82739</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33076</t>
+          <t>33211</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60285</t>
+          <t>62538</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88431</t>
+          <t>89155</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131547</t>
+          <t>133179</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1077144</t>
+          <t>1076270</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1110022</t>
+          <t>1108610</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>706372</t>
+          <t>704119</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>733581</t>
+          <t>733446</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1794120</t>
+          <t>1792488</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1837236</t>
+          <t>1836512</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10532</t>
+          <t>10616</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27811</t>
+          <t>28217</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>79017</t>
+          <t>79515</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>118684</t>
+          <t>115549</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>95227</t>
+          <t>96073</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136900</t>
+          <t>137256</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>482785</t>
+          <t>482379</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>500064</t>
+          <t>499980</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>642838</t>
+          <t>645973</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>682505</t>
+          <t>682007</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1135218</t>
+          <t>1134862</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1176891</t>
+          <t>1176045</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,45%</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7826</t>
+          <t>6055</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>120365</t>
+          <t>123367</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>169680</t>
+          <t>171330</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>125626</t>
+          <t>123295</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>170994</t>
+          <t>169674</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259056</t>
+          <t>260827</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>939671</t>
+          <t>938021</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>988986</t>
+          <t>985984</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1205239</t>
+          <t>1206559</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1250607</t>
+          <t>1252938</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>91,04%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>101221</t>
+          <t>101278</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>147631</t>
+          <t>146210</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>292109</t>
+          <t>297154</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>367271</t>
+          <t>368601</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>406276</t>
+          <t>409268</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>493248</t>
+          <t>496019</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3274279</t>
+          <t>3275700</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3320689</t>
+          <t>3320632</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3182854</t>
+          <t>3181524</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3258016</t>
+          <t>3252971</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6478787</t>
+          <t>6476016</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6565759</t>
+          <t>6562767</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,13%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22289</t>
+          <t>21658</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9296</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26161</t>
+          <t>25954</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19411</t>
+          <t>19725</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41600</t>
+          <t>41932</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406803</t>
+          <t>407434</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>422415</t>
+          <t>422826</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>320894</t>
+          <t>321101</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>337759</t>
+          <t>338318</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>734547</t>
+          <t>734215</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>756736</t>
+          <t>756422</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>12289</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5242</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20680</t>
+          <t>20404</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9893</t>
+          <t>9646</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27954</t>
+          <t>27884</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>364675</t>
+          <t>364938</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>375270</t>
+          <t>375294</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>351593</t>
+          <t>351869</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>367031</t>
+          <t>366833</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>721546</t>
+          <t>721616</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>739607</t>
+          <t>739854</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6892</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21641</t>
+          <t>22490</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15553</t>
+          <t>15568</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35737</t>
+          <t>35239</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26882</t>
+          <t>25764</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51974</t>
+          <t>52044</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>500273</t>
+          <t>499424</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515022</t>
+          <t>514584</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>130386</t>
+          <t>130884</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>150570</t>
+          <t>150555</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>636062</t>
+          <t>635992</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>661154</t>
+          <t>662272</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,26%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28726</t>
+          <t>28669</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53848</t>
+          <t>53082</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37914</t>
+          <t>38137</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67131</t>
+          <t>65007</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73468</t>
+          <t>71411</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>110688</t>
+          <t>109503</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1095790</t>
+          <t>1096556</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1120912</t>
+          <t>1120969</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>758745</t>
+          <t>760869</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>787962</t>
+          <t>787739</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1864826</t>
+          <t>1866011</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1902046</t>
+          <t>1904103</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24238</t>
+          <t>25288</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45476</t>
+          <t>46444</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71614</t>
+          <t>70976</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>108328</t>
+          <t>106939</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>104313</t>
+          <t>103322</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>146198</t>
+          <t>146330</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>575230</t>
+          <t>574262</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>596468</t>
+          <t>595418</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>629916</t>
+          <t>631305</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>666630</t>
+          <t>667268</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1212752</t>
+          <t>1212620</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1254637</t>
+          <t>1255628</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>101711</t>
+          <t>104512</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>147503</t>
+          <t>148127</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>105080</t>
+          <t>106030</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>147476</t>
+          <t>152135</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>280714</t>
+          <t>281452</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>934522</t>
+          <t>933898</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>980314</t>
+          <t>977513</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1221694</t>
+          <t>1217035</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1264090</t>
+          <t>1263140</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,26%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>87037</t>
+          <t>88498</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>125343</t>
+          <t>130367</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>284270</t>
+          <t>279945</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>358850</t>
+          <t>355873</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>380574</t>
+          <t>382840</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>466870</t>
+          <t>463680</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3260379</t>
+          <t>3255355</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3298685</t>
+          <t>3297224</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3172746</t>
+          <t>3175723</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3247326</t>
+          <t>3251651</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6450448</t>
+          <t>6453638</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6536744</t>
+          <t>6534478</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,47%</t>
         </is>
       </c>
     </row>
@@ -5997,32 +5997,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>18505</t>
+          <t>21301</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>14047</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27320</t>
+          <t>31285</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6032,32 +6032,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>38461</t>
+          <t>42404</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30318</t>
+          <t>33255</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49494</t>
+          <t>54133</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6067,32 +6067,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>56966</t>
+          <t>63705</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46620</t>
+          <t>51568</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70994</t>
+          <t>77475</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -6110,32 +6110,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>486707</t>
+          <t>529317</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>477892</t>
+          <t>519333</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>493157</t>
+          <t>536571</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6145,32 +6145,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>409006</t>
+          <t>446007</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>397973</t>
+          <t>434278</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>417149</t>
+          <t>455156</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6180,32 +6180,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>895713</t>
+          <t>975324</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>881685</t>
+          <t>961554</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>906059</t>
+          <t>987461</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -6223,17 +6223,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6258,17 +6258,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6340,32 +6340,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20256</t>
+          <t>21113</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13121</t>
+          <t>13988</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28911</t>
+          <t>30293</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6375,32 +6375,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43223</t>
+          <t>47752</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33293</t>
+          <t>38297</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53139</t>
+          <t>59030</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6410,17 +6410,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>63479</t>
+          <t>68866</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53239</t>
+          <t>55872</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77347</t>
+          <t>84193</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -6453,32 +6453,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>431957</t>
+          <t>462099</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>423302</t>
+          <t>452919</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>439092</t>
+          <t>469224</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6488,32 +6488,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>339357</t>
+          <t>375391</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>329441</t>
+          <t>364113</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>349287</t>
+          <t>384846</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6523,17 +6523,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>771314</t>
+          <t>837489</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>757446</t>
+          <t>822162</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>781554</t>
+          <t>850483</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,84%</t>
         </is>
       </c>
     </row>
@@ -6566,17 +6566,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6601,17 +6601,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6683,32 +6683,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>39089</t>
+          <t>41787</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14120</t>
+          <t>31190</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68330</t>
+          <t>54251</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6718,32 +6718,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30390</t>
+          <t>33670</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23121</t>
+          <t>26115</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38938</t>
+          <t>43275</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6753,32 +6753,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>69479</t>
+          <t>75457</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29680</t>
+          <t>61678</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>103547</t>
+          <t>91611</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -6796,32 +6796,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>629175</t>
+          <t>429825</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>599934</t>
+          <t>417361</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>654144</t>
+          <t>440422</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6831,32 +6831,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>136521</t>
+          <t>153827</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127973</t>
+          <t>144222</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>143790</t>
+          <t>161382</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6866,32 +6866,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>765696</t>
+          <t>583652</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>731628</t>
+          <t>567498</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>805495</t>
+          <t>597431</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -6909,17 +6909,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6944,17 +6944,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7026,32 +7026,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>100372</t>
+          <t>106086</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85391</t>
+          <t>89715</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119446</t>
+          <t>125876</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7061,32 +7061,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>84395</t>
+          <t>93789</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46053</t>
+          <t>80464</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>112540</t>
+          <t>109738</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7096,32 +7096,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>184767</t>
+          <t>199875</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125804</t>
+          <t>178009</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>215155</t>
+          <t>225314</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -7139,32 +7139,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>934447</t>
+          <t>1025757</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>915373</t>
+          <t>1005967</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>949428</t>
+          <t>1042128</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7174,32 +7174,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>893699</t>
+          <t>767422</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>865554</t>
+          <t>751473</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>932041</t>
+          <t>780747</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7209,32 +7209,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1828145</t>
+          <t>1793179</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1797757</t>
+          <t>1767740</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1887108</t>
+          <t>1815045</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>91,07%</t>
         </is>
       </c>
     </row>
@@ -7252,17 +7252,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7287,17 +7287,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7322,17 +7322,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7369,32 +7369,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>43654</t>
+          <t>46019</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31983</t>
+          <t>35076</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55631</t>
+          <t>58579</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7404,32 +7404,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>178488</t>
+          <t>190189</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>136699</t>
+          <t>172176</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>210075</t>
+          <t>209803</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7439,32 +7439,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>222141</t>
+          <t>236207</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>182212</t>
+          <t>214376</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>250407</t>
+          <t>260534</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -7482,32 +7482,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>431392</t>
+          <t>521945</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>419415</t>
+          <t>509385</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>443063</t>
+          <t>532888</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7517,32 +7517,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>662847</t>
+          <t>640661</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>631260</t>
+          <t>621047</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>704636</t>
+          <t>658674</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7552,32 +7552,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1094240</t>
+          <t>1162607</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1065974</t>
+          <t>1138280</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1134169</t>
+          <t>1184438</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>84,67%</t>
         </is>
       </c>
     </row>
@@ -7595,17 +7595,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7630,17 +7630,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7665,17 +7665,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7697,7 +7697,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7712,32 +7712,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8561</t>
+          <t>8058</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7747,67 +7747,67 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>131226</t>
+          <t>141881</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>115970</t>
+          <t>126782</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>147630</t>
+          <t>160207</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>15,02%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>18,98%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>145608</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>126758</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>164747</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>13,46%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>11,72%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>15,23%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>19,39%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>134936</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>119699</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>153984</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>13,47%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>11,95%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -7825,32 +7825,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>236797</t>
+          <t>233501</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>231946</t>
+          <t>229170</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239072</t>
+          <t>235859</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7860,67 +7860,67 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>630145</t>
+          <t>702400</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>613741</t>
+          <t>684074</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>645401</t>
+          <t>717499</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
+          <t>84,98%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1012</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>935901</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>916762</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>954751</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>86,54%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>84,77%</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>866942</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>847894</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>882179</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>86,53%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>84,63%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>
@@ -7938,17 +7938,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7973,17 +7973,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8055,32 +8055,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>225586</t>
+          <t>240032</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>174142</t>
+          <t>212587</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>259342</t>
+          <t>270593</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8090,32 +8090,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>506182</t>
+          <t>549685</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>415797</t>
+          <t>515779</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>556967</t>
+          <t>585174</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8125,32 +8125,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>731769</t>
+          <t>789717</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>640071</t>
+          <t>747410</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>788847</t>
+          <t>838922</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -8168,32 +8168,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3150474</t>
+          <t>3202444</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3116718</t>
+          <t>3171883</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3201918</t>
+          <t>3229889</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8203,32 +8203,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3071576</t>
+          <t>3085708</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3020791</t>
+          <t>3050219</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3161961</t>
+          <t>3119614</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6222049</t>
+          <t>6288152</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6164971</t>
+          <t>6238947</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6313747</t>
+          <t>6330459</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>89,44%</t>
         </is>
       </c>
     </row>
@@ -8281,17 +8281,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8316,17 +8316,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
